--- a/feedback_surveys/048_senior_home_delivery_feedback--feedback_surveys.xlsx
+++ b/feedback_surveys/048_senior_home_delivery_feedback--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Form submitted by</t>
+          <t>Form submitted by (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Satisfaction with delivery service</t>
+          <t>Delivery Service Satisfied</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>recipient_satisfaction</t>
+          <t>recipient_satisfaction_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Satisfaction with meal quality</t>
+          <t>Recipient Satisfaction 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>recipient_feedback</t>
+          <t>recipient_feedback_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Feedback from recipient</t>
+          <t>Recipient Feedback 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>delivery_service_satisfaction</t>
+          <t>delivery_service_satisfaction_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Satisfaction with delivery service</t>
+          <t>Delivery Service Satisfaction 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>recipient_satisfaction</t>
+          <t>recipient_satisfaction_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Satisfaction with meal quality</t>
+          <t>Recipient Satisfaction 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Recipient Comments</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>recipient_name</t>
+          <t>recipient_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Recipient name</t>
+          <t>Recipient Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>recipient_email</t>
+          <t>recipient_email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Recipient email</t>
+          <t>Recipient Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>delivery_service_email</t>
+          <t>delivery_service_email_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Delivery service email</t>
+          <t>Delivery Service Email 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1385,7 +1385,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,7 +1436,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>delivery_service_satisfaction_choices</t>
+          <t>delivery_service_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>delivery_service_satisfaction_choices</t>
+          <t>delivery_service_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>delivery_service_satisfaction_choices</t>
+          <t>delivery_service_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>delivery_service_satisfaction_choices</t>
+          <t>delivery_service_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>delivery_service_satisfaction_choices</t>
+          <t>delivery_service_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1572,7 +1572,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_3_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1589,7 +1589,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_3_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_3_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1623,7 +1623,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>recipient_satisfaction_choices</t>
+          <t>recipient_satisfaction_3_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
